--- a/result/TEMPORAL_TEMPORAL_ts-400_tssi-10_vth-1.0_tc-20_tw-80_tfs-80_tfd-80_outlier_train-tc.xlsx
+++ b/result/TEMPORAL_TEMPORAL_ts-400_tssi-10_vth-1.0_tc-20_tw-80_tfs-80_tfd-80_outlier_train-tc.xlsx
@@ -393,7 +393,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1127000004053116</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -410,7 +410,7 @@
         <v>20</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1127000004053116</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -427,7 +427,7 @@
         <v>30</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1127000004053116</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -444,7 +444,7 @@
         <v>40</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1127000004053116</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -461,7 +461,7 @@
         <v>50</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1127000004053116</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -478,7 +478,7 @@
         <v>60</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1127000004053116</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -495,7 +495,7 @@
         <v>70</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1127000004053116</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -512,7 +512,7 @@
         <v>80</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1127000004053116</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -529,13 +529,13 @@
         <v>90</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1127000004053116</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="C10" t="n">
-        <v>142.0395</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>142.0395</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -546,13 +546,13 @@
         <v>100</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1127000004053116</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="C11" t="n">
-        <v>830.9343</v>
+        <v>0.2213</v>
       </c>
       <c r="D11" t="n">
-        <v>830.9343</v>
+        <v>0.2213</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -563,13 +563,13 @@
         <v>110</v>
       </c>
       <c r="B12" t="n">
-        <v>0.1127000004053116</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="C12" t="n">
-        <v>1942.9455</v>
+        <v>20.9702</v>
       </c>
       <c r="D12" t="n">
-        <v>1942.9455</v>
+        <v>20.9702</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -580,13 +580,13 @@
         <v>120</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1127000004053116</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="C13" t="n">
-        <v>4685.7617</v>
+        <v>607.1154</v>
       </c>
       <c r="D13" t="n">
-        <v>4685.7617</v>
+        <v>607.1154</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -597,13 +597,13 @@
         <v>130</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1127000004053116</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="C14" t="n">
-        <v>5672.6751</v>
+        <v>4487.492</v>
       </c>
       <c r="D14" t="n">
-        <v>5672.6751</v>
+        <v>4487.492</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -614,13 +614,13 @@
         <v>140</v>
       </c>
       <c r="B15" t="n">
-        <v>0.1127000004053116</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="C15" t="n">
-        <v>6407.7411</v>
+        <v>17658.206</v>
       </c>
       <c r="D15" t="n">
-        <v>6407.7411</v>
+        <v>17658.206</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -631,13 +631,13 @@
         <v>150</v>
       </c>
       <c r="B16" t="n">
-        <v>0.1127000004053116</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="C16" t="n">
-        <v>6930.9693</v>
+        <v>47930.2028</v>
       </c>
       <c r="D16" t="n">
-        <v>6930.9693</v>
+        <v>47930.2028</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -648,13 +648,13 @@
         <v>160</v>
       </c>
       <c r="B17" t="n">
-        <v>0.1127000004053116</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="C17" t="n">
-        <v>7282.9062</v>
+        <v>93929.4623</v>
       </c>
       <c r="D17" t="n">
-        <v>7282.9062</v>
+        <v>93929.4623</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -665,16 +665,16 @@
         <v>170</v>
       </c>
       <c r="B18" t="n">
-        <v>0.9873999953269958</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="C18" t="n">
-        <v>8211.689899999999</v>
+        <v>93932.163</v>
       </c>
       <c r="D18" t="n">
-        <v>7282.9062</v>
+        <v>93929.4623</v>
       </c>
       <c r="E18" t="n">
-        <v>928.7837</v>
+        <v>2.7007</v>
       </c>
     </row>
     <row r="19">
@@ -682,16 +682,16 @@
         <v>180</v>
       </c>
       <c r="B19" t="n">
-        <v>0.9944000244140625</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="C19" t="n">
-        <v>9426.1126</v>
+        <v>93995.2187</v>
       </c>
       <c r="D19" t="n">
-        <v>7282.9062</v>
+        <v>93929.4623</v>
       </c>
       <c r="E19" t="n">
-        <v>2143.2064</v>
+        <v>65.7564</v>
       </c>
     </row>
     <row r="20">
@@ -699,16 +699,16 @@
         <v>190</v>
       </c>
       <c r="B20" t="n">
-        <v>0.995199978351593</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="C20" t="n">
-        <v>10731.3301</v>
+        <v>94655.8095</v>
       </c>
       <c r="D20" t="n">
-        <v>7282.9062</v>
+        <v>93929.4623</v>
       </c>
       <c r="E20" t="n">
-        <v>3448.4239</v>
+        <v>726.3472</v>
       </c>
     </row>
     <row r="21">
@@ -716,16 +716,16 @@
         <v>200</v>
       </c>
       <c r="B21" t="n">
-        <v>0.9951000213623047</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="C21" t="n">
-        <v>11845.0575</v>
+        <v>97663.511</v>
       </c>
       <c r="D21" t="n">
-        <v>7282.9062</v>
+        <v>93929.4623</v>
       </c>
       <c r="E21" t="n">
-        <v>4562.1513</v>
+        <v>3734.0487</v>
       </c>
     </row>
     <row r="22">
@@ -733,16 +733,16 @@
         <v>210</v>
       </c>
       <c r="B22" t="n">
-        <v>0.9952999949455261</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="C22" t="n">
-        <v>12673.522</v>
+        <v>106387.7441</v>
       </c>
       <c r="D22" t="n">
-        <v>7282.9062</v>
+        <v>93929.4623</v>
       </c>
       <c r="E22" t="n">
-        <v>5390.6158</v>
+        <v>12458.2818</v>
       </c>
     </row>
     <row r="23">
@@ -750,16 +750,16 @@
         <v>220</v>
       </c>
       <c r="B23" t="n">
-        <v>0.9950000047683716</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="C23" t="n">
-        <v>13242.8726</v>
+        <v>126501.1876</v>
       </c>
       <c r="D23" t="n">
-        <v>7282.9062</v>
+        <v>93929.4623</v>
       </c>
       <c r="E23" t="n">
-        <v>5959.9664</v>
+        <v>32571.7253</v>
       </c>
     </row>
     <row r="24">
@@ -767,16 +767,16 @@
         <v>230</v>
       </c>
       <c r="B24" t="n">
-        <v>0.9951000213623047</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="C24" t="n">
-        <v>13617.1562</v>
+        <v>156367.9094</v>
       </c>
       <c r="D24" t="n">
-        <v>7282.9062</v>
+        <v>93929.4623</v>
       </c>
       <c r="E24" t="n">
-        <v>6334.25</v>
+        <v>62438.4471</v>
       </c>
     </row>
     <row r="25">
@@ -784,16 +784,16 @@
         <v>240</v>
       </c>
       <c r="B25" t="n">
-        <v>0.9948999881744385</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="C25" t="n">
-        <v>13857.6689</v>
+        <v>186888.2482</v>
       </c>
       <c r="D25" t="n">
-        <v>7282.9062</v>
+        <v>93929.4623</v>
       </c>
       <c r="E25" t="n">
-        <v>6574.7627</v>
+        <v>92958.7859</v>
       </c>
     </row>
     <row r="26">
@@ -801,16 +801,16 @@
         <v>250</v>
       </c>
       <c r="B26" t="n">
-        <v>0.9948999881744385</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="C26" t="n">
-        <v>13857.6689</v>
+        <v>186898.673</v>
       </c>
       <c r="D26" t="n">
-        <v>7282.9062</v>
+        <v>93929.4623</v>
       </c>
       <c r="E26" t="n">
-        <v>6574.7627</v>
+        <v>92958.7859</v>
       </c>
     </row>
     <row r="27">
@@ -818,16 +818,16 @@
         <v>260</v>
       </c>
       <c r="B27" t="n">
-        <v>0.9948999881744385</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="C27" t="n">
-        <v>13857.6689</v>
+        <v>187125.9323</v>
       </c>
       <c r="D27" t="n">
-        <v>7282.9062</v>
+        <v>93929.4623</v>
       </c>
       <c r="E27" t="n">
-        <v>6574.7627</v>
+        <v>92958.7859</v>
       </c>
     </row>
     <row r="28">
@@ -835,16 +835,16 @@
         <v>270</v>
       </c>
       <c r="B28" t="n">
-        <v>0.9948999881744385</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="C28" t="n">
-        <v>13857.6689</v>
+        <v>188953.3678</v>
       </c>
       <c r="D28" t="n">
-        <v>7282.9062</v>
+        <v>93929.4623</v>
       </c>
       <c r="E28" t="n">
-        <v>6574.7627</v>
+        <v>92958.7859</v>
       </c>
     </row>
     <row r="29">
@@ -852,16 +852,16 @@
         <v>280</v>
       </c>
       <c r="B29" t="n">
-        <v>0.9948999881744385</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="C29" t="n">
-        <v>13857.6689</v>
+        <v>195890.2619</v>
       </c>
       <c r="D29" t="n">
-        <v>7282.9062</v>
+        <v>93929.4623</v>
       </c>
       <c r="E29" t="n">
-        <v>6574.7627</v>
+        <v>92958.7859</v>
       </c>
     </row>
     <row r="30">
@@ -869,16 +869,16 @@
         <v>290</v>
       </c>
       <c r="B30" t="n">
-        <v>0.9948999881744385</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="C30" t="n">
-        <v>13857.6689</v>
+        <v>209124.1869</v>
       </c>
       <c r="D30" t="n">
-        <v>7282.9062</v>
+        <v>93929.4623</v>
       </c>
       <c r="E30" t="n">
-        <v>6574.7627</v>
+        <v>92958.7859</v>
       </c>
     </row>
     <row r="31">
@@ -886,16 +886,16 @@
         <v>300</v>
       </c>
       <c r="B31" t="n">
-        <v>0.9948999881744385</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="C31" t="n">
-        <v>13857.6689</v>
+        <v>223628.849</v>
       </c>
       <c r="D31" t="n">
-        <v>7282.9062</v>
+        <v>93929.4623</v>
       </c>
       <c r="E31" t="n">
-        <v>6574.7627</v>
+        <v>92958.7859</v>
       </c>
     </row>
     <row r="32">
@@ -903,16 +903,16 @@
         <v>310</v>
       </c>
       <c r="B32" t="n">
-        <v>0.9948999881744385</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="C32" t="n">
-        <v>13857.6689</v>
+        <v>234888.0714</v>
       </c>
       <c r="D32" t="n">
-        <v>7282.9062</v>
+        <v>93929.4623</v>
       </c>
       <c r="E32" t="n">
-        <v>6574.7627</v>
+        <v>92958.7859</v>
       </c>
     </row>
     <row r="33">
@@ -920,16 +920,16 @@
         <v>320</v>
       </c>
       <c r="B33" t="n">
-        <v>0.9948999881744385</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="C33" t="n">
-        <v>13857.6689</v>
+        <v>242328.8521</v>
       </c>
       <c r="D33" t="n">
-        <v>7282.9062</v>
+        <v>93929.4623</v>
       </c>
       <c r="E33" t="n">
-        <v>6574.7627</v>
+        <v>92958.7859</v>
       </c>
     </row>
     <row r="34">
@@ -937,16 +937,16 @@
         <v>330</v>
       </c>
       <c r="B34" t="n">
-        <v>0.9948999881744385</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="C34" t="n">
-        <v>13857.6689</v>
+        <v>242342.8545</v>
       </c>
       <c r="D34" t="n">
-        <v>7282.9062</v>
+        <v>93929.4623</v>
       </c>
       <c r="E34" t="n">
-        <v>6574.7627</v>
+        <v>92958.7859</v>
       </c>
     </row>
     <row r="35">
@@ -954,16 +954,16 @@
         <v>340</v>
       </c>
       <c r="B35" t="n">
-        <v>0.9948999881744385</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="C35" t="n">
-        <v>13857.6689</v>
+        <v>242618.2045</v>
       </c>
       <c r="D35" t="n">
-        <v>7282.9062</v>
+        <v>93929.4623</v>
       </c>
       <c r="E35" t="n">
-        <v>6574.7627</v>
+        <v>92958.7859</v>
       </c>
     </row>
     <row r="36">
@@ -971,16 +971,16 @@
         <v>350</v>
       </c>
       <c r="B36" t="n">
-        <v>0.9948999881744385</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="C36" t="n">
-        <v>13857.6689</v>
+        <v>244192.8937</v>
       </c>
       <c r="D36" t="n">
-        <v>7282.9062</v>
+        <v>93929.4623</v>
       </c>
       <c r="E36" t="n">
-        <v>6574.7627</v>
+        <v>92958.7859</v>
       </c>
     </row>
     <row r="37">
@@ -988,16 +988,16 @@
         <v>360</v>
       </c>
       <c r="B37" t="n">
-        <v>0.9948999881744385</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="C37" t="n">
-        <v>13857.6689</v>
+        <v>247934.6718</v>
       </c>
       <c r="D37" t="n">
-        <v>7282.9062</v>
+        <v>93929.4623</v>
       </c>
       <c r="E37" t="n">
-        <v>6574.7627</v>
+        <v>92958.7859</v>
       </c>
     </row>
     <row r="38">
@@ -1005,16 +1005,16 @@
         <v>370</v>
       </c>
       <c r="B38" t="n">
-        <v>0.9948999881744385</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="C38" t="n">
-        <v>13857.6689</v>
+        <v>253072.0125</v>
       </c>
       <c r="D38" t="n">
-        <v>7282.9062</v>
+        <v>93929.4623</v>
       </c>
       <c r="E38" t="n">
-        <v>6574.7627</v>
+        <v>92958.7859</v>
       </c>
     </row>
     <row r="39">
@@ -1022,16 +1022,16 @@
         <v>380</v>
       </c>
       <c r="B39" t="n">
-        <v>0.9948999881744385</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="C39" t="n">
-        <v>13857.6689</v>
+        <v>258022.0129</v>
       </c>
       <c r="D39" t="n">
-        <v>7282.9062</v>
+        <v>93929.4623</v>
       </c>
       <c r="E39" t="n">
-        <v>6574.7627</v>
+        <v>92958.7859</v>
       </c>
     </row>
     <row r="40">
@@ -1039,16 +1039,16 @@
         <v>390</v>
       </c>
       <c r="B40" t="n">
-        <v>0.9948999881744385</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="C40" t="n">
-        <v>13857.6689</v>
+        <v>261863.0207</v>
       </c>
       <c r="D40" t="n">
-        <v>7282.9062</v>
+        <v>93929.4623</v>
       </c>
       <c r="E40" t="n">
-        <v>6574.7627</v>
+        <v>92958.7859</v>
       </c>
     </row>
     <row r="41">
@@ -1056,16 +1056,16 @@
         <v>400</v>
       </c>
       <c r="B41" t="n">
-        <v>0.9948999881744385</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="C41" t="n">
-        <v>13857.6689</v>
+        <v>264502.1227</v>
       </c>
       <c r="D41" t="n">
-        <v>7282.9062</v>
+        <v>93929.4623</v>
       </c>
       <c r="E41" t="n">
-        <v>6574.7627</v>
+        <v>92958.7859</v>
       </c>
     </row>
   </sheetData>
